--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123335845</v>
+        <v>123336238</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566962</v>
+        <v>566935</v>
       </c>
       <c r="R2" t="n">
-        <v>7031755</v>
+        <v>7031817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123336238</v>
+        <v>123336512</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566935</v>
+        <v>566854</v>
       </c>
       <c r="R3" t="n">
-        <v>7031817</v>
+        <v>7031882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123336512</v>
+        <v>123335845</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566854</v>
+        <v>566962</v>
       </c>
       <c r="R4" t="n">
-        <v>7031882</v>
+        <v>7031755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,6 +1028,946 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123438494</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bodbäcken, Bodbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566787</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7031914</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123439167</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bodbäcken, Bodbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>566766</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7032026</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123438606</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90957</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodbäcken, Bodbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566793</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7031906</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123438119</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodbäcken, Bodbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566744</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7031881</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska &amp; äldre spår</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123439465</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90953</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodbäcken, Bodbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566819</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7031976</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123440029</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56683</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bodbäcken, Bodbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566904</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7031729</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123439398</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90975</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bodbäcken, Bodbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>566814</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7031990</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123439315</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90953</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bodbäcken, Bodbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>566813</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7032000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>123335845</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123438494</v>
+        <v>123440029</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>56683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566787</v>
+        <v>566904</v>
       </c>
       <c r="R5" t="n">
-        <v>7031914</v>
+        <v>7031729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1275,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123438606</v>
+        <v>123438119</v>
       </c>
       <c r="B7" t="n">
-        <v>90957</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,34 +1286,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566793</v>
+        <v>566744</v>
       </c>
       <c r="R7" t="n">
-        <v>7031906</v>
+        <v>7031881</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1360,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska &amp; äldre spår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123438119</v>
+        <v>123439315</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>90953</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566744</v>
+        <v>566813</v>
       </c>
       <c r="R8" t="n">
-        <v>7031881</v>
+        <v>7032000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,12 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska &amp; äldre spår</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123439465</v>
+        <v>123438494</v>
       </c>
       <c r="B9" t="n">
-        <v>90953</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,34 +1520,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566819</v>
+        <v>566787</v>
       </c>
       <c r="R9" t="n">
-        <v>7031976</v>
+        <v>7031914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,7 +1594,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123440029</v>
+        <v>123439398</v>
       </c>
       <c r="B10" t="n">
-        <v>56683</v>
+        <v>90975</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,27 +1642,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1666,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566904</v>
+        <v>566814</v>
       </c>
       <c r="R10" t="n">
-        <v>7031729</v>
+        <v>7031990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1720,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123439398</v>
+        <v>123438606</v>
       </c>
       <c r="B11" t="n">
-        <v>90975</v>
+        <v>90957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,43 +1763,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566814</v>
+        <v>566793</v>
       </c>
       <c r="R11" t="n">
-        <v>7031990</v>
+        <v>7031906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,7 +1859,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123439315</v>
+        <v>123439465</v>
       </c>
       <c r="B12" t="n">
         <v>90953</v>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566813</v>
+        <v>566819</v>
       </c>
       <c r="R12" t="n">
-        <v>7032000</v>
+        <v>7031976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123336238</v>
+        <v>123336512</v>
       </c>
       <c r="B2" t="n">
         <v>57481</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566935</v>
+        <v>566854</v>
       </c>
       <c r="R2" t="n">
-        <v>7031817</v>
+        <v>7031882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123336512</v>
+        <v>123336238</v>
       </c>
       <c r="B3" t="n">
         <v>57481</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566854</v>
+        <v>566935</v>
       </c>
       <c r="R3" t="n">
-        <v>7031882</v>
+        <v>7031817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -922,7 +922,7 @@
         <v>123335845</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123440029</v>
+        <v>123439167</v>
       </c>
       <c r="B5" t="n">
-        <v>56683</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1067,7 +1067,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566904</v>
+        <v>566766</v>
       </c>
       <c r="R5" t="n">
-        <v>7031729</v>
+        <v>7032026</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123439167</v>
+        <v>123438119</v>
       </c>
       <c r="B6" t="n">
         <v>57481</v>
@@ -1193,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566766</v>
+        <v>566744</v>
       </c>
       <c r="R6" t="n">
-        <v>7032026</v>
+        <v>7031881</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1243,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall, färska &amp; äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123438119</v>
+        <v>123440029</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>56683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,16 +1291,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1306,7 +1311,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566744</v>
+        <v>566904</v>
       </c>
       <c r="R7" t="n">
-        <v>7031881</v>
+        <v>7031729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1355,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,12 +1365,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska &amp; äldre spår</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123439315</v>
+        <v>123438494</v>
       </c>
       <c r="B8" t="n">
-        <v>90953</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,34 +1408,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566813</v>
+        <v>566787</v>
       </c>
       <c r="R8" t="n">
-        <v>7032000</v>
+        <v>7031914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1472,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1482,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123438494</v>
+        <v>123438606</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>90963</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,39 +1530,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566787</v>
+        <v>566793</v>
       </c>
       <c r="R9" t="n">
-        <v>7031914</v>
+        <v>7031906</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1589,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1599,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123439398</v>
+        <v>123439465</v>
       </c>
       <c r="B10" t="n">
-        <v>90975</v>
+        <v>90959</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,43 +1642,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566814</v>
+        <v>566819</v>
       </c>
       <c r="R10" t="n">
-        <v>7031990</v>
+        <v>7031976</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123438606</v>
+        <v>123439398</v>
       </c>
       <c r="B11" t="n">
-        <v>90957</v>
+        <v>90981</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,34 +1754,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566793</v>
+        <v>566814</v>
       </c>
       <c r="R11" t="n">
-        <v>7031906</v>
+        <v>7031990</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123439465</v>
+        <v>123439315</v>
       </c>
       <c r="B12" t="n">
-        <v>90953</v>
+        <v>90959</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566819</v>
+        <v>566813</v>
       </c>
       <c r="R12" t="n">
-        <v>7031976</v>
+        <v>7032000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123336512</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>123336238</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         <v>123335845</v>
       </c>
       <c r="B4" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123439398</v>
+        <v>123440029</v>
       </c>
       <c r="B5" t="n">
-        <v>90984</v>
+        <v>56689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,31 +1047,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1080,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566814</v>
+        <v>566904</v>
       </c>
       <c r="R5" t="n">
-        <v>7031990</v>
+        <v>7031729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123439465</v>
+        <v>123439167</v>
       </c>
       <c r="B6" t="n">
-        <v>90962</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,34 +1164,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566819</v>
+        <v>566766</v>
       </c>
       <c r="R6" t="n">
-        <v>7031976</v>
+        <v>7032026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1238,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123439167</v>
+        <v>123438606</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>90983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566766</v>
+        <v>566793</v>
       </c>
       <c r="R7" t="n">
-        <v>7032026</v>
+        <v>7031906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,12 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,7 +1385,7 @@
         <v>123438119</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1511,7 +1507,7 @@
         <v>123438494</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1630,10 +1626,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123438606</v>
+        <v>123439315</v>
       </c>
       <c r="B10" t="n">
-        <v>90966</v>
+        <v>90979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,21 +1642,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1670,10 +1666,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566793</v>
+        <v>566813</v>
       </c>
       <c r="R10" t="n">
-        <v>7031906</v>
+        <v>7032000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1701,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1711,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123439315</v>
+        <v>123439398</v>
       </c>
       <c r="B11" t="n">
-        <v>90962</v>
+        <v>91001</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,34 +1754,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566813</v>
+        <v>566814</v>
       </c>
       <c r="R11" t="n">
-        <v>7032000</v>
+        <v>7031990</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1822,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1832,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440029</v>
+        <v>123439465</v>
       </c>
       <c r="B12" t="n">
-        <v>56683</v>
+        <v>90979</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,39 +1875,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566904</v>
+        <v>566819</v>
       </c>
       <c r="R12" t="n">
-        <v>7031729</v>
+        <v>7031976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123438606</v>
+        <v>123438119</v>
       </c>
       <c r="B7" t="n">
-        <v>90983</v>
+        <v>57487</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,34 +1286,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566793</v>
+        <v>566744</v>
       </c>
       <c r="R7" t="n">
-        <v>7031906</v>
+        <v>7031881</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1360,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska &amp; äldre spår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123438119</v>
+        <v>123438606</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566744</v>
+        <v>566793</v>
       </c>
       <c r="R8" t="n">
-        <v>7031881</v>
+        <v>7031906</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,12 +1477,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska &amp; äldre spår</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123336512</v>
+        <v>123335845</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566854</v>
+        <v>566962</v>
       </c>
       <c r="R2" t="n">
-        <v>7031882</v>
+        <v>7031755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123336238</v>
+        <v>123336512</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566935</v>
+        <v>566854</v>
       </c>
       <c r="R3" t="n">
-        <v>7031817</v>
+        <v>7031882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123335845</v>
+        <v>123336238</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566962</v>
+        <v>566935</v>
       </c>
       <c r="R4" t="n">
-        <v>7031755</v>
+        <v>7031817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123440029</v>
+        <v>123438606</v>
       </c>
       <c r="B5" t="n">
-        <v>56689</v>
+        <v>90988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566904</v>
+        <v>566793</v>
       </c>
       <c r="R5" t="n">
-        <v>7031729</v>
+        <v>7031906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123439167</v>
+        <v>123438494</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1193,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566766</v>
+        <v>566787</v>
       </c>
       <c r="R6" t="n">
-        <v>7032026</v>
+        <v>7031914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,7 +1268,7 @@
         <v>123438119</v>
       </c>
       <c r="B7" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1392,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123438606</v>
+        <v>123439167</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,34 +1403,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566793</v>
+        <v>566766</v>
       </c>
       <c r="R8" t="n">
-        <v>7031906</v>
+        <v>7032026</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,7 +1477,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123438494</v>
+        <v>123439398</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>91006</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,27 +1525,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1549,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566787</v>
+        <v>566814</v>
       </c>
       <c r="R9" t="n">
-        <v>7031914</v>
+        <v>7031990</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1584,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1594,12 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123439315</v>
+        <v>123439465</v>
       </c>
       <c r="B10" t="n">
-        <v>90979</v>
+        <v>90984</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566813</v>
+        <v>566819</v>
       </c>
       <c r="R10" t="n">
-        <v>7032000</v>
+        <v>7031976</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123439398</v>
+        <v>123439315</v>
       </c>
       <c r="B11" t="n">
-        <v>91001</v>
+        <v>90984</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,43 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566814</v>
+        <v>566813</v>
       </c>
       <c r="R11" t="n">
-        <v>7031990</v>
+        <v>7032000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123439465</v>
+        <v>123440029</v>
       </c>
       <c r="B12" t="n">
-        <v>90979</v>
+        <v>56692</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,34 +1870,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566819</v>
+        <v>566904</v>
       </c>
       <c r="R12" t="n">
-        <v>7031976</v>
+        <v>7031729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123335845</v>
+        <v>123336238</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566962</v>
+        <v>566935</v>
       </c>
       <c r="R2" t="n">
-        <v>7031755</v>
+        <v>7031817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123336512</v>
+        <v>123335845</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566854</v>
+        <v>566962</v>
       </c>
       <c r="R3" t="n">
-        <v>7031882</v>
+        <v>7031755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123336238</v>
+        <v>123336512</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566935</v>
+        <v>566854</v>
       </c>
       <c r="R4" t="n">
-        <v>7031817</v>
+        <v>7031882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123438606</v>
+        <v>123438494</v>
       </c>
       <c r="B5" t="n">
-        <v>90988</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1047,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566793</v>
+        <v>566787</v>
       </c>
       <c r="R5" t="n">
-        <v>7031906</v>
+        <v>7031914</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123438494</v>
+        <v>123439398</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,27 +1169,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566787</v>
+        <v>566814</v>
       </c>
       <c r="R6" t="n">
-        <v>7031914</v>
+        <v>7031990</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123438119</v>
+        <v>123439167</v>
       </c>
       <c r="B7" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566744</v>
+        <v>566766</v>
       </c>
       <c r="R7" t="n">
-        <v>7031881</v>
+        <v>7032026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,12 +1364,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall, färska &amp; äldre spår</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123439167</v>
+        <v>123439465</v>
       </c>
       <c r="B8" t="n">
-        <v>57490</v>
+        <v>90986</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,39 +1412,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566766</v>
+        <v>566819</v>
       </c>
       <c r="R8" t="n">
-        <v>7032026</v>
+        <v>7031976</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1467,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1477,12 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123439398</v>
+        <v>123438119</v>
       </c>
       <c r="B9" t="n">
-        <v>91006</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,31 +1524,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1558,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566814</v>
+        <v>566744</v>
       </c>
       <c r="R9" t="n">
-        <v>7031990</v>
+        <v>7031881</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1598,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska &amp; äldre spår</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123439465</v>
+        <v>123438606</v>
       </c>
       <c r="B10" t="n">
-        <v>90984</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,21 +1646,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566819</v>
+        <v>566793</v>
       </c>
       <c r="R10" t="n">
-        <v>7031976</v>
+        <v>7031906</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123439315</v>
+        <v>123440029</v>
       </c>
       <c r="B11" t="n">
-        <v>90984</v>
+        <v>56692</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,34 +1758,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566813</v>
+        <v>566904</v>
       </c>
       <c r="R11" t="n">
-        <v>7032000</v>
+        <v>7031729</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1822,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1832,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440029</v>
+        <v>123439315</v>
       </c>
       <c r="B12" t="n">
-        <v>56692</v>
+        <v>90986</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,39 +1875,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566904</v>
+        <v>566813</v>
       </c>
       <c r="R12" t="n">
-        <v>7031729</v>
+        <v>7032000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123336238</v>
+        <v>123336512</v>
       </c>
       <c r="B2" t="n">
         <v>57491</v>
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566935</v>
+        <v>566854</v>
       </c>
       <c r="R2" t="n">
-        <v>7031817</v>
+        <v>7031882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123335845</v>
+        <v>123336238</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566962</v>
+        <v>566935</v>
       </c>
       <c r="R3" t="n">
-        <v>7031755</v>
+        <v>7031817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123336512</v>
+        <v>123335845</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566854</v>
+        <v>566962</v>
       </c>
       <c r="R4" t="n">
-        <v>7031882</v>
+        <v>7031755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123438494</v>
+        <v>123439315</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566787</v>
+        <v>566813</v>
       </c>
       <c r="R5" t="n">
-        <v>7031914</v>
+        <v>7032000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123439398</v>
+        <v>123438494</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,31 +1159,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1202,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566814</v>
+        <v>566787</v>
       </c>
       <c r="R6" t="n">
-        <v>7031990</v>
+        <v>7031914</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1396,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123439465</v>
+        <v>123438119</v>
       </c>
       <c r="B8" t="n">
-        <v>90986</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,34 +1403,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566819</v>
+        <v>566744</v>
       </c>
       <c r="R8" t="n">
-        <v>7031976</v>
+        <v>7031881</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1467,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1477,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall, färska &amp; äldre spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1509,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123438119</v>
+        <v>123439398</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,27 +1525,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1553,10 +1558,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566744</v>
+        <v>566814</v>
       </c>
       <c r="R9" t="n">
-        <v>7031881</v>
+        <v>7031990</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,12 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall, färska &amp; äldre spår</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1742,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123440029</v>
+        <v>123439465</v>
       </c>
       <c r="B11" t="n">
-        <v>56692</v>
+        <v>90986</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,39 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566904</v>
+        <v>566819</v>
       </c>
       <c r="R11" t="n">
-        <v>7031729</v>
+        <v>7031976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123439315</v>
+        <v>123440029</v>
       </c>
       <c r="B12" t="n">
-        <v>90986</v>
+        <v>56692</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,34 +1870,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566813</v>
+        <v>566904</v>
       </c>
       <c r="R12" t="n">
-        <v>7032000</v>
+        <v>7031729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123336512</v>
+        <v>123335845</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566854</v>
+        <v>566962</v>
       </c>
       <c r="R2" t="n">
-        <v>7031882</v>
+        <v>7031755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123336238</v>
+        <v>123336512</v>
       </c>
       <c r="B3" t="n">
         <v>57491</v>
@@ -842,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566935</v>
+        <v>566854</v>
       </c>
       <c r="R3" t="n">
-        <v>7031817</v>
+        <v>7031882</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -919,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123335845</v>
+        <v>123336238</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566962</v>
+        <v>566935</v>
       </c>
       <c r="R4" t="n">
-        <v>7031755</v>
+        <v>7031817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123439315</v>
+        <v>123438606</v>
       </c>
       <c r="B5" t="n">
-        <v>90986</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566813</v>
+        <v>566793</v>
       </c>
       <c r="R5" t="n">
-        <v>7032000</v>
+        <v>7031906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123438494</v>
+        <v>123440029</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566787</v>
+        <v>566904</v>
       </c>
       <c r="R6" t="n">
-        <v>7031914</v>
+        <v>7031729</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1509,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123439398</v>
+        <v>123439315</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>90986</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,43 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566814</v>
+        <v>566813</v>
       </c>
       <c r="R9" t="n">
-        <v>7031990</v>
+        <v>7032000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123438606</v>
+        <v>123438494</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,34 +1632,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566793</v>
+        <v>566787</v>
       </c>
       <c r="R10" t="n">
-        <v>7031906</v>
+        <v>7031914</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1706,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123439465</v>
+        <v>123439398</v>
       </c>
       <c r="B11" t="n">
-        <v>90986</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,34 +1754,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566819</v>
+        <v>566814</v>
       </c>
       <c r="R11" t="n">
-        <v>7031976</v>
+        <v>7031990</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1822,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1832,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440029</v>
+        <v>123439465</v>
       </c>
       <c r="B12" t="n">
-        <v>56692</v>
+        <v>90986</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,39 +1875,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566904</v>
+        <v>566819</v>
       </c>
       <c r="R12" t="n">
-        <v>7031729</v>
+        <v>7031976</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123335845</v>
+        <v>123336512</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566962</v>
+        <v>566854</v>
       </c>
       <c r="R2" t="n">
-        <v>7031755</v>
+        <v>7031882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123336512</v>
+        <v>123336238</v>
       </c>
       <c r="B3" t="n">
         <v>57491</v>
@@ -832,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566854</v>
+        <v>566935</v>
       </c>
       <c r="R3" t="n">
-        <v>7031882</v>
+        <v>7031817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123336238</v>
+        <v>123335845</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566935</v>
+        <v>566962</v>
       </c>
       <c r="R4" t="n">
-        <v>7031817</v>
+        <v>7031755</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:55</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123440029</v>
+        <v>123439167</v>
       </c>
       <c r="B6" t="n">
-        <v>56692</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566904</v>
+        <v>566766</v>
       </c>
       <c r="R6" t="n">
-        <v>7031729</v>
+        <v>7032026</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123439167</v>
+        <v>123439398</v>
       </c>
       <c r="B7" t="n">
-        <v>57491</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,27 +1281,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1305,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566766</v>
+        <v>566814</v>
       </c>
       <c r="R7" t="n">
-        <v>7032026</v>
+        <v>7031990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1504,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123439315</v>
+        <v>123438494</v>
       </c>
       <c r="B9" t="n">
-        <v>90986</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,34 +1524,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566813</v>
+        <v>566787</v>
       </c>
       <c r="R9" t="n">
-        <v>7032000</v>
+        <v>7031914</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1598,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123438494</v>
+        <v>123439315</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,39 +1646,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566787</v>
+        <v>566813</v>
       </c>
       <c r="R10" t="n">
-        <v>7031914</v>
+        <v>7032000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1696,7 +1705,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,12 +1715,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1742,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123439398</v>
+        <v>123439465</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>90986</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1754,43 +1758,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566814</v>
+        <v>566819</v>
       </c>
       <c r="R11" t="n">
-        <v>7031990</v>
+        <v>7031976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123439465</v>
+        <v>123440029</v>
       </c>
       <c r="B12" t="n">
-        <v>90986</v>
+        <v>56692</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,34 +1870,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566819</v>
+        <v>566904</v>
       </c>
       <c r="R12" t="n">
-        <v>7031976</v>
+        <v>7031729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41904-2024 artfynd.xlsx
+++ b/artfynd/A 41904-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123336512</v>
+        <v>123335845</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566854</v>
+        <v>566962</v>
       </c>
       <c r="R2" t="n">
-        <v>7031882</v>
+        <v>7031755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -919,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123335845</v>
+        <v>123336512</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566962</v>
+        <v>566854</v>
       </c>
       <c r="R4" t="n">
-        <v>7031755</v>
+        <v>7031882</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123438606</v>
+        <v>123439465</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>90986</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566793</v>
+        <v>566819</v>
       </c>
       <c r="R5" t="n">
-        <v>7031906</v>
+        <v>7031976</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123439167</v>
+        <v>123440029</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1179,7 +1179,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566766</v>
+        <v>566904</v>
       </c>
       <c r="R6" t="n">
-        <v>7032026</v>
+        <v>7031729</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:46</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123439398</v>
+        <v>123438494</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,31 +1276,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1314,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566814</v>
+        <v>566787</v>
       </c>
       <c r="R7" t="n">
-        <v>7031990</v>
+        <v>7031914</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1508,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123438494</v>
+        <v>123439315</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>90986</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,39 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566787</v>
+        <v>566813</v>
       </c>
       <c r="R9" t="n">
-        <v>7031914</v>
+        <v>7032000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1598,12 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123439315</v>
+        <v>123439167</v>
       </c>
       <c r="B10" t="n">
-        <v>90986</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,34 +1632,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bodbäcken, Bodbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566813</v>
+        <v>566766</v>
       </c>
       <c r="R10" t="n">
-        <v>7032000</v>
+        <v>7032026</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1705,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1715,7 +1706,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123439465</v>
+        <v>123438606</v>
       </c>
       <c r="B11" t="n">
-        <v>90986</v>
+        <v>90990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1758,21 +1754,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1782,10 +1778,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566819</v>
+        <v>566793</v>
       </c>
       <c r="R11" t="n">
-        <v>7031976</v>
+        <v>7031906</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1817,7 +1813,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1823,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123440029</v>
+        <v>123439398</v>
       </c>
       <c r="B12" t="n">
-        <v>56692</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,27 +1866,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566904</v>
+        <v>566814</v>
       </c>
       <c r="R12" t="n">
-        <v>7031729</v>
+        <v>7031990</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
